--- a/diseases/d021/2000-2004.xlsx
+++ b/diseases/d021/2000-2004.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -1901,9 +1898,6 @@
       <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -2741,9 +2735,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -3581,9 +3572,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4421,9 +4409,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5261,9 +5246,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6101,9 +6083,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6941,9 +6920,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -7781,9 +7757,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8621,9 +8594,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9461,9 +9431,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10301,9 +10268,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -11141,9 +11105,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -11685,9 +11646,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -12129,9 +12087,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -12673,9 +12628,6 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -13117,9 +13069,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -13661,9 +13610,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -14105,9 +14051,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14649,9 +14592,6 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -15093,9 +15033,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -15637,9 +15574,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -16081,9 +16015,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -16625,9 +16556,6 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -17069,9 +16997,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -17613,9 +17538,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -18057,9 +17979,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -18601,9 +18520,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19045,9 +18961,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -19589,9 +19502,6 @@
       <c r="O115" t="n">
         <v>1</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -20033,9 +19943,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -20577,9 +20484,6 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -21021,9 +20925,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -21565,9 +21466,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -22009,9 +21907,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -22553,9 +22448,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -22997,9 +22889,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -23541,9 +23430,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -23985,9 +23871,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -24529,9 +24412,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -24973,9 +24853,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -25517,9 +25394,6 @@
       <c r="O151" t="n">
         <v>2</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.004228408433091266</v>
       </c>
@@ -25961,9 +25835,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -26505,9 +26376,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -26949,9 +26817,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -27493,9 +27358,6 @@
       <c r="O163" t="n">
         <v>1</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -27937,9 +27799,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -28481,9 +28340,6 @@
       <c r="O169" t="n">
         <v>1</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -28925,9 +28781,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -29469,9 +29322,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -29913,9 +29763,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -30457,9 +30304,6 @@
       <c r="O181" t="n">
         <v>2</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.004228408433091266</v>
       </c>
@@ -30901,9 +30745,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -31445,9 +31286,6 @@
       <c r="O187" t="n">
         <v>1</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -31889,9 +31727,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -32433,9 +32268,6 @@
       <c r="O193" t="n">
         <v>1</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -32877,9 +32709,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -33421,9 +33250,6 @@
       <c r="O199" t="n">
         <v>1</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -33865,9 +33691,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -34409,9 +34232,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -34853,9 +34673,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -35397,9 +35214,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -35989,9 +35803,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -36533,9 +36344,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -37125,9 +36933,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -37669,9 +37474,6 @@
       <c r="O225" t="n">
         <v>3</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -38261,9 +38063,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -38805,9 +38604,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -39397,9 +39193,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -39941,9 +39734,6 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -40533,9 +40323,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -41077,9 +40864,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -41669,9 +41453,6 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0</v>
       </c>
@@ -42213,9 +41994,6 @@
       <c r="O253" t="n">
         <v>2</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0.004209271465503426</v>
       </c>
@@ -42805,9 +42583,6 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0</v>
       </c>
@@ -43349,9 +43124,6 @@
       <c r="O260" t="n">
         <v>4</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.008418542931006853</v>
       </c>
@@ -43941,9 +43713,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0</v>
       </c>
@@ -44485,9 +44254,6 @@
       <c r="O267" t="n">
         <v>3</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -45077,9 +44843,6 @@
       <c r="O271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -45621,9 +45384,6 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0</v>
       </c>
@@ -46213,9 +45973,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -46757,9 +46514,6 @@
       <c r="O281" t="n">
         <v>1</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -47349,9 +47103,6 @@
       <c r="O285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
@@ -47893,9 +47644,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -48485,9 +48233,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -49029,9 +48774,6 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -49621,9 +49363,6 @@
       <c r="O299" t="n">
         <v>3</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -50165,9 +49904,6 @@
       <c r="O302" t="n">
         <v>1</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -50757,9 +50493,6 @@
       <c r="O306" t="n">
         <v>1</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -51301,9 +51034,6 @@
       <c r="O309" t="n">
         <v>0</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0</v>
       </c>
@@ -51893,9 +51623,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -52437,9 +52164,6 @@
       <c r="O316" t="n">
         <v>1</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -53029,9 +52753,6 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
@@ -53573,9 +53294,6 @@
       <c r="O323" t="n">
         <v>0</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0</v>
       </c>
@@ -54165,9 +53883,6 @@
       <c r="O327" t="n">
         <v>0</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0</v>
       </c>
@@ -54709,9 +54424,6 @@
       <c r="O330" t="n">
         <v>0</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0</v>
       </c>
@@ -55301,9 +55013,6 @@
       <c r="O334" t="n">
         <v>1</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -55845,9 +55554,6 @@
       <c r="O337" t="n">
         <v>1</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -56437,9 +56143,6 @@
       <c r="O341" t="n">
         <v>2</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -56981,9 +56684,6 @@
       <c r="O344" t="n">
         <v>5</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.01048282299823602</v>
       </c>
@@ -57573,9 +57273,6 @@
       <c r="O348" t="n">
         <v>0</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0</v>
       </c>
@@ -58117,9 +57814,6 @@
       <c r="O351" t="n">
         <v>1</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -58709,9 +58403,6 @@
       <c r="O355" t="n">
         <v>2</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -59253,9 +58944,6 @@
       <c r="O358" t="n">
         <v>1</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -59845,9 +59533,6 @@
       <c r="O362" t="n">
         <v>1</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -60389,9 +60074,6 @@
       <c r="O365" t="n">
         <v>4</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0.008386258398588819</v>
       </c>
@@ -60981,9 +60663,6 @@
       <c r="O369" t="n">
         <v>1</v>
       </c>
-      <c r="Q369" t="n">
-        <v>0</v>
-      </c>
       <c r="R369" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -61524,9 +61203,6 @@
       </c>
       <c r="O372" t="n">
         <v>2</v>
-      </c>
-      <c r="Q372" t="n">
-        <v>0</v>
       </c>
       <c r="R372" t="n">
         <v>0.004193129199294409</v>
